--- a/AAII_Financials/Quarterly/LYEL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LYEL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
   <si>
     <t>LYEL</t>
   </si>
@@ -656,132 +656,136 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -822,52 +826,55 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>48400</v>
       </c>
-      <c r="R8" s="3">
-        <v>0</v>
-      </c>
       <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>35700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>600</v>
-      </c>
-      <c r="U8" s="3">
-        <v>2800</v>
       </c>
       <c r="V8" s="3">
         <v>2800</v>
       </c>
       <c r="W8" s="3">
+        <v>2800</v>
+      </c>
+      <c r="X8" s="3">
         <v>2600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1300</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -952,8 +959,11 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -994,11 +1004,11 @@
         <v>0</v>
       </c>
       <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1038,8 +1048,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,94 +1083,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E12" s="3">
         <v>36600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>52200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>28200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>34900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>43400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>48700</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>39500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>40300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>43200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>47000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>43800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>47500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>44600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>45300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>39200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>40100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>39700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>19300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>31400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>46400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>41500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>35100</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>24500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>97200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>25500</v>
       </c>
-      <c r="AC12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,68 +1259,71 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>64500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
-        <v>3800</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I14" s="3">
         <v>1300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>135600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>11500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
         <v>2900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>10000</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>5000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
         <v>36400</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1316,8 +1336,8 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1328,40 +1348,43 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E15" s="3">
         <v>2300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>5000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>5100</v>
       </c>
       <c r="N15" s="3">
         <v>5100</v>
@@ -1370,11 +1393,11 @@
         <v>5100</v>
       </c>
       <c r="P15" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Q15" s="3">
         <v>5000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1414,8 +1437,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E17" s="3">
         <v>44300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>61500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>37300</v>
       </c>
-      <c r="G17" s="3">
-        <v>43300</v>
-      </c>
       <c r="H17" s="3">
+        <v>43200</v>
+      </c>
+      <c r="I17" s="3">
         <v>56100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>61800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>50500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>51500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55600</v>
-      </c>
-      <c r="M17" s="3">
-        <v>59100</v>
       </c>
       <c r="N17" s="3">
         <v>59100</v>
       </c>
       <c r="O17" s="3">
+        <v>59100</v>
+      </c>
+      <c r="P17" s="3">
         <v>65900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>62600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>63200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>71400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>73000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>69100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>86800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>51900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>65300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>57800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>41800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>37900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>105700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>34300</v>
       </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-47300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-44300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-61500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-37300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-43300</v>
-      </c>
       <c r="H18" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="I18" s="3">
         <v>-56100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-61700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-50500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-51500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-55600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-59100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-59000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-65900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-62600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-14800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-71400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-37300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-68500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-84000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-49100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-62700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-55400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-39500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-36800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-102600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-33000</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,180 +1680,187 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-17900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>17500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3700</v>
       </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-44700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-24000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-76500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-39500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-39000</v>
-      </c>
       <c r="H21" s="3">
+        <v>-38900</v>
+      </c>
+      <c r="I21" s="3">
         <v>-51300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-56200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-45900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-47300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-51000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-54500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-52400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-61200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-56400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-65600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-32200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-64000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-79100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-44800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-59600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-53100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-37400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-34600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-99700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-28500</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1863,8 +1903,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1905,94 +1945,100 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-24200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-140700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-38800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-42700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-52200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-191900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-44600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-45800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-60700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-52900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-50900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-63900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-8400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-70300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-36300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-68100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-83700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-48900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-62600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-38900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-35700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2035,8 +2081,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2077,8 +2123,11 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-24200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-140700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-38800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-42700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-52200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-191900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-44600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-45800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-60700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-52900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-50900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-63900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-8400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-70300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-36300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-68100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-83700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-48900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-62600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-38900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-35700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-24200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-140700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-38800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-42700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-52200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-191900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-44600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-45800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-60700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-52900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-50900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-63900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-70300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-36300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-68100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-83700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-48900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-62600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-38900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-35700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2568,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,180 +2746,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>17900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-17500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-24200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-140700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-38800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-42700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-52200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-191900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-44600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-45800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-60700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-52900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-50900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-63900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-70300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-36300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-68100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-83700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-48900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-62600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-38900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-35700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-24200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-140700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-38800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-42700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-52200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-191900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-44600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-45800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-60700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-52900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-50900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-63900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-70300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-36300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-68100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-83700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-48900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-62600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-38900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-35700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,77 +3264,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E41" s="3">
         <v>90800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>60200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>123600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>98800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>120300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>105600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>100300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>125700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>145600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>286200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>224400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>109400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>123600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>116300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>205700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>222600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>293800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>393500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>564400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>244400</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3264,77 +3351,80 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>131100</v>
+      </c>
+      <c r="E42" s="3">
         <v>163300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>187000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>196000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>178000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>180800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>264900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>340200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>357700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>400700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>400600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>289200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>371400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>503300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>516600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>531800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>449800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>391300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>321000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>225400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>260100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>360600</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3440,11 @@
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3394,8 +3487,8 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -3436,8 +3529,11 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3480,8 +3576,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3522,8 +3618,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3566,33 +3665,33 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>11100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4800</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,77 +3707,80 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>213500</v>
+      </c>
+      <c r="E46" s="3">
         <v>267300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>260900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>328200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>282200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>309200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>379600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>450000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>499800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>534200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>554700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>586900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>606400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>624400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>651300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>659700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>666800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>625700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>626300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>631100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>834800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>609700</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3694,77 +3796,80 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E47" s="3">
         <v>26000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>19000</v>
       </c>
       <c r="F47" s="3">
         <v>19000</v>
       </c>
       <c r="G47" s="3">
+        <v>19000</v>
+      </c>
+      <c r="H47" s="3">
         <v>39100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>47900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>32000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>39100</v>
-      </c>
-      <c r="K47" s="3">
-        <v>19000</v>
       </c>
       <c r="L47" s="3">
         <v>19000</v>
       </c>
       <c r="M47" s="3">
+        <v>19000</v>
+      </c>
+      <c r="N47" s="3">
         <v>48500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>54700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>69000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>90200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>115000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>144500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>178400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>271100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>330500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>401000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>233700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>118700</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3780,77 +3885,80 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E48" s="3">
         <v>50500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>53600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>56600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>60100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>67800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>72900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>124700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>130800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>136500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>142300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>148700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>155200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>161000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>166300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>169800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>172500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>171400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>166600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>163100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>158100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>144900</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3974,11 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3952,8 +4063,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,34 +4241,37 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E52" s="3">
         <v>6800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>4100</v>
       </c>
       <c r="G52" s="3">
         <v>4100</v>
       </c>
       <c r="H52" s="3">
+        <v>4100</v>
+      </c>
+      <c r="I52" s="3">
         <v>4900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>4500</v>
       </c>
       <c r="L52" s="3">
         <v>4500</v>
@@ -4160,41 +4280,41 @@
         <v>4500</v>
       </c>
       <c r="N52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="O52" s="3">
         <v>4700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3900</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4210,8 +4330,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,77 +4419,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>311200</v>
+      </c>
+      <c r="E54" s="3">
         <v>350600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>340100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>408000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>385500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>429800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>490900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>619200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>654100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>694200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>750000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>795000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>835400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>880500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>937600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>977300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1021700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1072100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1127400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1198300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1229900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>877200</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4382,8 +4508,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,77 +4576,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>5500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>4200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>3200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>3500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,53 +4663,56 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E58" s="3">
         <v>9400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>8200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>8000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4800</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4618,77 +4752,80 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16500</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>5500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>33100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>46400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>46000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>34500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>43500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>55800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>58800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>49700</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,77 +4841,80 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E60" s="3">
         <v>36900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>49400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>31900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>36900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>41300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>30900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>34500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>35100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>34400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>37000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>51200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>50300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>41100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>46700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>59300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>63700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>56800</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,53 +4930,56 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E61" s="3">
         <v>39500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>41900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>44300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>46600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>48900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>53300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>55200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>56900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>58600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>60200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>61800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4876,8 +5019,11 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4888,65 +5034,65 @@
         <v>500</v>
       </c>
       <c r="F62" s="3">
+        <v>500</v>
+      </c>
+      <c r="G62" s="3">
         <v>2700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>67300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>106000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>103300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>149800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>150900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>152600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>144200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>143500</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4962,8 +5108,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,77 +5375,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>77300</v>
+      </c>
+      <c r="E66" s="3">
         <v>77000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>91900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>78800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>86500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>93300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>108000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>88500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>87600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>91100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>95100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>97400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>98500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>96600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>104300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>157200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>153600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>190900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>197600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>211900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>207900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>200300</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5306,8 +5464,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5576,11 +5744,11 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
         <v>1011000</v>
       </c>
-      <c r="Y70" s="3">
-        <v>0</v>
-      </c>
       <c r="Z70" s="3">
         <v>0</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,77 +5853,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1688500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1643700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1619600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1478800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1440000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1397300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1345100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1153200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1108600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1062800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1002100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-949200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-898300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-834400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-767500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-759100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-688800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-652500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-584400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-500700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-451800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-389200</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5768,8 +5942,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,77 +6209,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>233800</v>
+      </c>
+      <c r="E76" s="3">
         <v>273700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>248200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>329100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>298900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>336500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>382800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>530700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>566500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>603200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>655000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>697600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>736900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>783800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>833300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>820000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>868000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>881200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>929800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>986500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1022000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-334000</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6112,8 +6298,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AD80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-24200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-140700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-38800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-42700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-52200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-191900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-44600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-45800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-60700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-52900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-50900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-63900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-70300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-36300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-68100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-83700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-48900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-62600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-55000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-38900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-35700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-100700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,28 +6605,29 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E83" s="3">
         <v>3400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5000</v>
-      </c>
-      <c r="I83" s="3">
-        <v>5100</v>
       </c>
       <c r="J83" s="3">
         <v>5100</v>
@@ -6437,64 +6636,67 @@
         <v>5100</v>
       </c>
       <c r="L83" s="3">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="M83" s="3">
         <v>5000</v>
       </c>
       <c r="N83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O83" s="3">
         <v>4600</v>
-      </c>
-      <c r="O83" s="3">
-        <v>4200</v>
       </c>
       <c r="P83" s="3">
         <v>4200</v>
       </c>
       <c r="Q83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="R83" s="3">
         <v>5000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4600</v>
-      </c>
-      <c r="S83" s="3">
-        <v>4200</v>
       </c>
       <c r="T83" s="3">
         <v>4200</v>
       </c>
       <c r="U83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="V83" s="3">
         <v>4600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>800</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-33900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-38500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-32300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-34500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-54700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-47200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-35000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-38100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-42000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-40600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-37700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-39200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-46200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-40300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-37100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-44300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-47900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-33200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-25500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-33900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-33600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-26700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-21600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-88900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-23600</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,94 +7261,98 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
       </c>
       <c r="I91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-24900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6900</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E94" s="3">
         <v>17400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-31400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>3300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>12600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>69500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>53500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>45000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>22000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>99700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>152900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>32200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>46600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-57100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>25000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-26100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-73900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-144900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-39500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>136700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>32400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-89900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-99900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-116100</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7650,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7461,8 +7695,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7503,8 +7737,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,94 +8004,100 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
         <v>51700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>50000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>900</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>7400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>393500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>300</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>476400</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7891,8 +8140,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7933,90 +8182,96 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E102" s="3">
         <v>30600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-63400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>24800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-33100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-140600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>61800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>114900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-89400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-71400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-99700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-170900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>320100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>104000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>6000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-111500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-188800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>336700</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
